--- a/Server/src/main/resources/static/excel插入数据_说中文.xlsx
+++ b/Server/src/main/resources/static/excel插入数据_说中文.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="48">
   <si>
     <t>商品名</t>
   </si>
@@ -50,10 +50,10 @@
     <t>消费类别</t>
   </si>
   <si>
-    <t>示例记录</t>
-  </si>
-  <si>
-    <t>202501010001</t>
+    <t>炒饭</t>
+  </si>
+  <si>
+    <t>21011101</t>
   </si>
   <si>
     <t>学校食堂</t>
@@ -63,6 +63,114 @@
   </si>
   <si>
     <t>餐饮消费</t>
+  </si>
+  <si>
+    <t>参考书《数据结构》</t>
+  </si>
+  <si>
+    <t>21011123</t>
+  </si>
+  <si>
+    <t>校内书店</t>
+  </si>
+  <si>
+    <t>微信</t>
+  </si>
+  <si>
+    <t>学习用品</t>
+  </si>
+  <si>
+    <t>电影票</t>
+  </si>
+  <si>
+    <t>21011215</t>
+  </si>
+  <si>
+    <t>校外电影院</t>
+  </si>
+  <si>
+    <t>支付宝</t>
+  </si>
+  <si>
+    <t>娱乐消费</t>
+  </si>
+  <si>
+    <t>公交卡充值</t>
+  </si>
+  <si>
+    <t>21011307</t>
+  </si>
+  <si>
+    <t>公交站点</t>
+  </si>
+  <si>
+    <t>现金</t>
+  </si>
+  <si>
+    <t>交通出行</t>
+  </si>
+  <si>
+    <t>水费缴纳</t>
+  </si>
+  <si>
+    <t>21011449</t>
+  </si>
+  <si>
+    <t>校内宿舍服务中心</t>
+  </si>
+  <si>
+    <t>生活服务</t>
+  </si>
+  <si>
+    <t>文具套装</t>
+  </si>
+  <si>
+    <t>21011541</t>
+  </si>
+  <si>
+    <t>校内超市</t>
+  </si>
+  <si>
+    <t>咖啡</t>
+  </si>
+  <si>
+    <t>21011633</t>
+  </si>
+  <si>
+    <t>学校咖啡厅</t>
+  </si>
+  <si>
+    <t>课程补习费</t>
+  </si>
+  <si>
+    <t>21011725</t>
+  </si>
+  <si>
+    <t>校外培训机构</t>
+  </si>
+  <si>
+    <t>银行卡</t>
+  </si>
+  <si>
+    <t>其他</t>
+  </si>
+  <si>
+    <t>小吃</t>
+  </si>
+  <si>
+    <t>21011747</t>
+  </si>
+  <si>
+    <t>校内小卖部</t>
+  </si>
+  <si>
+    <t>打印费</t>
+  </si>
+  <si>
+    <t>21011817</t>
+  </si>
+  <si>
+    <t>校内打印店</t>
   </si>
 </sst>
 </file>
@@ -683,17 +791,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1225,7 +1333,7 @@
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="22.4615384615385" customWidth="1"/>
-    <col min="2" max="2" width="14.1538461538462" customWidth="1"/>
+    <col min="2" max="2" width="14.1538461538462" style="1" customWidth="1"/>
     <col min="3" max="3" width="8.53846153846154" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="16.5384615384615" customWidth="1"/>
@@ -1234,10 +1342,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -1260,7 +1368,7 @@
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C2">
@@ -1269,7 +1377,7 @@
       <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="3">
         <v>45658.5208333333</v>
       </c>
       <c r="F2" t="s">
@@ -1279,32 +1387,212 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="5:5">
-      <c r="E3" s="2"/>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>56</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="3">
+        <v>45659.59375</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="4" spans="5:5">
-      <c r="E4" s="2"/>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="3">
+        <v>45660.8229166667</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="5" spans="5:5">
-      <c r="E5" s="2"/>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5">
+        <v>50</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="3">
+        <v>45661.3333333333</v>
+      </c>
+      <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="6" spans="5:5">
-      <c r="E6" s="2"/>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6">
+        <v>23.75</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="3">
+        <v>45662.4305555556</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="7" spans="5:5">
-      <c r="E7" s="2"/>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>15.5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="3">
+        <v>45663.3958333333</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="8" spans="5:5">
-      <c r="E8" s="2"/>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="3">
+        <v>45664.6666666667</v>
+      </c>
+      <c r="F8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="9" spans="5:5">
-      <c r="E9" s="2"/>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9">
+        <v>120</v>
+      </c>
+      <c r="D9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="3">
+        <v>45665.7395833333</v>
+      </c>
+      <c r="F9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="10" spans="5:5">
-      <c r="E10" s="2"/>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="3">
+        <v>45666.4583333333</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="11" spans="5:5">
-      <c r="E11" s="2"/>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="D11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="3">
+        <v>45667.6388888889</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="3">
